--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|DeviceRequest|ImmunizationRecommendation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -1046,7 +1046,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-specimen)
 </t>
   </si>
   <si>
@@ -1074,7 +1074,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1318,7 +1318,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-imagingstudy|Media|QuestionnaireResponse|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|MolecularSequence)
 </t>
   </si>
   <si>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-observationresultsradiology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
